--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI22"/>
+  <dimension ref="A1:AI27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46044.51041666666</v>
+        <v>46044.5</v>
       </c>
     </row>
     <row r="16">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46044.60416666666</v>
+        <v>46044.51041666666</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46044.625</v>
+        <v>46044.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46044.79166666666</v>
+        <v>46044.70833333334</v>
       </c>
     </row>
     <row r="22">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3013,102 +3013,697 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Portmore United</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Molynes United</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3" t="n">
+        <v>46044.70833333334</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Tivoli Gardens</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Racing United</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3" t="n">
+        <v>46044.70833333334</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Lincoln City</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Burton Albion</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="n">
+        <v>46044.70833333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="3" t="n">
-        <v>46044.89583333334</v>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3" t="n">
+        <v>46044.875</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CR Belouizdad</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3" t="n">
+        <v>46044.875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>JS Kabylie</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3" t="n">
+        <v>46044.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,14 +2087,14 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="M14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,14 +2206,14 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="M15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N15" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,14 +2087,14 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="M14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,14 +2206,14 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="M15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N15" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,14 +2087,14 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="M14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,14 +2206,14 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="M15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N15" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,14 +2087,14 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="M14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,14 +2206,14 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="M15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N15" t="n">
         <v>3</v>
       </c>
-      <c r="N15" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI27"/>
+  <dimension ref="A1:AI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46044.41666666666</v>
+        <v>46044.42708333334</v>
       </c>
     </row>
     <row r="12">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46044.42708333334</v>
+        <v>46044.4375</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46044.4375</v>
+        <v>46044.5</v>
       </c>
     </row>
     <row r="14">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,14 +2087,14 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="M14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46044.5</v>
+        <v>46044.51041666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46044.51041666666</v>
+        <v>46044.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46044.60416666666</v>
+        <v>46044.625</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46044.625</v>
+        <v>46044.70833333334</v>
       </c>
     </row>
     <row r="20">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46044.70833333334</v>
+        <v>46044.875</v>
       </c>
     </row>
     <row r="25">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3584,125 +3584,6 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46044.875</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46044</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>USM Alger</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>JS Kabylie</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="3" t="n">
         <v>46044.875</v>
       </c>
     </row>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,14 +1968,14 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="M13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N13" t="n">
         <v>3</v>
       </c>
-      <c r="N13" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,14 +2087,14 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="M14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,14 +1968,14 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="M13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N13" t="n">
         <v>3</v>
       </c>
-      <c r="N13" t="n">
-        <v>5.8</v>
-      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="M18" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="M13" t="n">
         <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="M14" t="n">
         <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="M13" t="n">
         <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="M14" t="n">
         <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.5</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.51041666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.58</v>
+        <v>3.17</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.4</v>
+        <v>4.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="T13" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.74</v>
+        <v>2.43</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.42</v>
+        <v>2.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3.17</v>
+        <v>2.58</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.22</v>
+        <v>6.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="S14" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V14" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.43</v>
+        <v>2.74</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.5</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="O13" t="n">
-        <v>3.17</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.22</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="S13" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD13" t="n">
         <v>1.11</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="M14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V14" t="n">
+        <v>9</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC14" t="n">
         <v>4.75</v>
       </c>
-      <c r="O14" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="AD14" t="n">
         <v>1.17</v>
       </c>
-      <c r="V14" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE14" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.5</v>
@@ -2572,34 +2572,34 @@
         <v>2.13</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y18" t="n">
         <v>1.6</v>
@@ -2608,28 +2608,28 @@
         <v>2.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46044.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="M13" t="n">
         <v>2.85</v>
       </c>
       <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V13" t="n">
+        <v>9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC13" t="n">
         <v>4.75</v>
       </c>
-      <c r="O13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="AD13" t="n">
         <v>1.17</v>
       </c>
-      <c r="V13" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="M14" t="n">
         <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.22</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S14" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.75</v>
+        <v>5.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.5</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="M13" t="n">
         <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.22</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.43</v>
+        <v>2.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.75</v>
+        <v>5.59</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="M14" t="n">
         <v>2.85</v>
       </c>
       <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V14" t="n">
+        <v>9</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC14" t="n">
         <v>4.75</v>
       </c>
-      <c r="O14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="AD14" t="n">
         <v>1.17</v>
       </c>
-      <c r="V14" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AE14" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.5</v>
@@ -2581,13 +2581,13 @@
         <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="S18" t="n">
         <v>2.02</v>
       </c>
       <c r="T18" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
         <v>1.16</v>
@@ -2596,10 +2596,10 @@
         <v>11</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Y18" t="n">
         <v>1.6</v>
@@ -2629,7 +2629,7 @@
         <v>1.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46044.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="M13" t="n">
         <v>2.85</v>
       </c>
       <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V13" t="n">
+        <v>9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC13" t="n">
         <v>4.75</v>
       </c>
-      <c r="O13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="AD13" t="n">
         <v>1.17</v>
       </c>
-      <c r="V13" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="M14" t="n">
         <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.22</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.75</v>
+        <v>5.59</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.5</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="N15" t="n">
         <v>4.67</v>
@@ -2218,61 +2218,61 @@
         <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.21</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.94</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.51041666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2334,64 +2334,64 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1977,7 +1977,7 @@
         <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="P13" t="n">
         <v>1.81</v>
@@ -1986,7 +1986,7 @@
         <v>4.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
         <v>2.26</v>
@@ -1995,10 +1995,10 @@
         <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
@@ -2019,16 +2019,16 @@
         <v>1.48</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG13" t="n">
         <v>1.33</v>
@@ -2099,19 +2099,19 @@
         <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="R14" t="n">
         <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="T14" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="U14" t="n">
         <v>1.17</v>
@@ -2144,7 +2144,7 @@
         <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="AF14" t="n">
         <v>1.49</v>
@@ -2153,7 +2153,7 @@
         <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.5</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2578,7 +2578,7 @@
         <v>1.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
         <v>1.68</v>
@@ -2587,7 +2587,7 @@
         <v>2.02</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="U18" t="n">
         <v>1.16</v>
@@ -2596,7 +2596,7 @@
         <v>11</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
         <v>1.11</v>
@@ -2611,19 +2611,19 @@
         <v>3.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AC18" t="n">
         <v>6.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AG18" t="n">
         <v>1.37</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="M13" t="n">
         <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="O13" t="n">
-        <v>3.17</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.22</v>
+        <v>6.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="V13" t="n">
-        <v>8.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.8</v>
+        <v>5.59</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="M14" t="n">
         <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>3.17</v>
       </c>
       <c r="P14" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.4</v>
+        <v>4.22</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="S14" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="T14" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V14" t="n">
-        <v>9.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.59</v>
+        <v>4.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.5</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>4.67</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>2.2</v>
@@ -2227,7 +2227,7 @@
         <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="T15" t="n">
         <v>2.78</v>
@@ -2245,13 +2245,13 @@
         <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
         <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
         <v>1.8</v>
@@ -2269,10 +2269,10 @@
         <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.51041666666</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.48</v>
+        <v>2.14</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2462,22 +2462,22 @@
         <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
         <v>3.82</v>
       </c>
       <c r="T17" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V17" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
@@ -2486,7 +2486,7 @@
         <v>1.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AA17" t="n">
         <v>1.42</v>
@@ -2501,16 +2501,16 @@
         <v>1.73</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="M10" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2206,19 +2206,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>4.67</v>
       </c>
       <c r="O15" t="n">
         <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
         <v>5</v>
@@ -2242,25 +2242,25 @@
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
         <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA15" t="n">
         <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
         <v>3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
         <v>1.8</v>
@@ -2269,7 +2269,7 @@
         <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
         <v>2.05</v>
@@ -2328,10 +2328,10 @@
         <v>2.14</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2453,31 +2453,31 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P17" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="Q17" t="n">
         <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="T17" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V17" t="n">
         <v>4.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
@@ -2486,7 +2486,7 @@
         <v>1.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
         <v>1.42</v>
@@ -2501,16 +2501,16 @@
         <v>1.73</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46044.70833333334</v>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46044.39583333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="M13" t="n">
         <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>3.17</v>
       </c>
       <c r="P13" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.4</v>
+        <v>4.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="T13" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.59</v>
+        <v>4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="M14" t="n">
         <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3.17</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.22</v>
+        <v>6.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>12</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.8</v>
+        <v>5.59</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.04</v>
+        <v>2.54</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.5</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2581,13 +2581,13 @@
         <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S18" t="n">
         <v>2.02</v>
       </c>
       <c r="T18" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
         <v>1.16</v>
@@ -2596,10 +2596,10 @@
         <v>11</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Y18" t="n">
         <v>1.6</v>
@@ -2614,16 +2614,16 @@
         <v>1.31</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.05</v>
+        <v>6.51</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AG18" t="n">
         <v>1.37</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="M4" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="N4" t="n">
-        <v>3.73</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="M5" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>3.73</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="M13" t="n">
         <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="O13" t="n">
-        <v>3.17</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.22</v>
+        <v>6.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.8</v>
+        <v>5.59</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.04</v>
+        <v>2.54</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="M14" t="n">
         <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>3.17</v>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.4</v>
+        <v>4.22</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>3.96</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.59</v>
+        <v>4.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.54</v>
+        <v>2.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.5</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="M4" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.73</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="M5" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="N5" t="n">
-        <v>3.73</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="M13" t="n">
         <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>3.17</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.4</v>
+        <v>4.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="T13" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>12</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.59</v>
+        <v>4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.54</v>
+        <v>2.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="M14" t="n">
         <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3.17</v>
+        <v>2.63</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.22</v>
+        <v>6.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.48</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.5</v>
@@ -2572,13 +2572,13 @@
         <v>2.13</v>
       </c>
       <c r="O18" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="P18" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R18" t="n">
         <v>1.7</v>
@@ -2593,7 +2593,7 @@
         <v>1.16</v>
       </c>
       <c r="V18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W18" t="n">
         <v>1.02</v>
@@ -2608,7 +2608,7 @@
         <v>2.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AB18" t="n">
         <v>1.31</v>
@@ -2617,7 +2617,7 @@
         <v>6.51</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE18" t="n">
         <v>2.38</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.3</v>
+        <v>2.37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>2.09</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46044.42708333334</v>
+        <v>46044.5</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46044.4375</v>
+        <v>46044.5</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="O13" t="n">
-        <v>3.17</v>
+        <v>2.2</v>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.22</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.26</v>
+        <v>2.94</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>8.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46044.5</v>
+        <v>46044.51041666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.79</v>
+        <v>1.14</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>6.5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.75</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>2.63</v>
+        <v>1.48</v>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>2.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>2.23</v>
+        <v>3.88</v>
       </c>
       <c r="T14" t="n">
-        <v>3.96</v>
+        <v>2.05</v>
       </c>
       <c r="U14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.17</v>
       </c>
-      <c r="V14" t="n">
-        <v>12</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
       <c r="X14" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.74</v>
+        <v>1.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.39</v>
+        <v>2.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.59</v>
+        <v>2.06</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.82</v>
+        <v>4.33</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46044.5</v>
+        <v>46044.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>4.67</v>
+        <v>2.69</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46044.51041666666</v>
+        <v>46044.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.14</v>
+        <v>3.73</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="N16" t="n">
-        <v>2.62</v>
+        <v>2.13</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.35</v>
+        <v>1.31</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46044.60416666666</v>
+        <v>46044.625</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2453,67 +2453,67 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46044.60416666666</v>
+        <v>46044.70833333334</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,76 +2563,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46044.625</v>
+        <v>46044.70833333334</v>
       </c>
     </row>
     <row r="19">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,80 +3035,80 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46044.70833333334</v>
+        <v>46044.875</v>
       </c>
     </row>
     <row r="23">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46044.70833333334</v>
+        <v>46044.875</v>
       </c>
     </row>
     <row r="24">
@@ -3346,244 +3346,6 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46044.875</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46044</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" s="3" t="n">
-        <v>46044.875</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46044</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>USM Alger</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>JS Kabylie</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="3" t="n">
         <v>46044.875</v>
       </c>
     </row>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.99</v>
       </c>
       <c r="M3" t="n">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>3.72</v>
       </c>
       <c r="O3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46044.39583333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="M4" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="N4" t="n">
-        <v>3.73</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.19</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
-        <v>2.81</v>
+        <v>4.58</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1730,25 +1730,25 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="N11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O11" t="n">
         <v>3</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.17</v>
-      </c>
       <c r="P11" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.22</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
         <v>2.26</v>
@@ -1760,7 +1760,7 @@
         <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="W11" t="n">
         <v>1.05</v>
@@ -1772,28 +1772,28 @@
         <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AD11" t="n">
         <v>1.11</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
         <v>1.48</v>
@@ -1849,70 +1849,70 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="N12" t="n">
-        <v>4.75</v>
+        <v>5.01</v>
       </c>
       <c r="O12" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="S12" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
         <v>12</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
         <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AA12" t="n">
         <v>2.74</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
         <v>5.59</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
         <v>1.82</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.14</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>2.69</v>
       </c>
       <c r="O14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>1.14</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.69</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2325,37 +2325,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.73</v>
+        <v>3.4</v>
       </c>
       <c r="M16" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="N16" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>4.85</v>
+        <v>5.1</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
         <v>1.7</v>
       </c>
       <c r="S16" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="U16" t="n">
         <v>1.16</v>
       </c>
       <c r="V16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
@@ -2364,10 +2364,10 @@
         <v>1.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AA16" t="n">
         <v>3.1</v>
@@ -2376,10 +2376,10 @@
         <v>1.31</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.51</v>
+        <v>6.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE16" t="n">
         <v>2.38</v>
@@ -2391,7 +2391,7 @@
         <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46044.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.99</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.94</v>
+        <v>4.2</v>
       </c>
       <c r="N3" t="n">
-        <v>3.72</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46044.39583333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="M4" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.73</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>2.19</v>
       </c>
       <c r="M5" t="n">
-        <v>4.58</v>
+        <v>2.81</v>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="M11" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1772,13 +1772,13 @@
         <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
         <v>4.85</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>5.01</v>
+        <v>4.75</v>
       </c>
       <c r="O12" t="n">
         <v>2.7</v>
@@ -1888,10 +1888,10 @@
         <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AA12" t="n">
         <v>2.74</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.14</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="N14" t="n">
-        <v>2.69</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.14</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>2.69</v>
       </c>
       <c r="O15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="M16" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="O16" t="n">
         <v>5.1</v>
@@ -2364,10 +2364,10 @@
         <v>1.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AA16" t="n">
         <v>3.1</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
         <v>2.1</v>
@@ -2459,13 +2459,13 @@
         <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.57</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
         <v>2.73</v>
@@ -2474,37 +2474,37 @@
         <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>6.35</v>
+        <v>5.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
         <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC17" t="n">
         <v>2.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
         <v>1.25</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.99</v>
       </c>
       <c r="M3" t="n">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>3.73</v>
       </c>
       <c r="O3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46044.39583333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="M4" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="N4" t="n">
-        <v>3.73</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.19</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>2.81</v>
+        <v>4.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="M6" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="M11" t="n">
         <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V11" t="n">
+        <v>12</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V11" t="n">
-        <v>10</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
         <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46044.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="M12" t="n">
         <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.59</v>
+        <v>4.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
         <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46044.5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="M3" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="N3" t="n">
-        <v>3.73</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="M4" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.73</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="M11" t="n">
         <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="T11" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.59</v>
+        <v>4.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
         <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46044.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
         <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>12</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V12" t="n">
-        <v>10</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
         <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46044.5</v>
@@ -1968,19 +1968,19 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="M13" t="n">
         <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P13" t="n">
         <v>2.2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
         <v>5</v>
@@ -1989,7 +1989,7 @@
         <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="T13" t="n">
         <v>2.78</v>
@@ -2001,7 +2001,7 @@
         <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.05</v>
@@ -2010,19 +2010,19 @@
         <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
         <v>1.8</v>
@@ -2031,7 +2031,7 @@
         <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
         <v>2.02</v>
@@ -2087,19 +2087,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="M14" t="n">
         <v>6.5</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O14" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="Q14" t="n">
         <v>9</v>
@@ -2108,10 +2108,10 @@
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="U14" t="n">
         <v>1.71</v>
@@ -2129,31 +2129,31 @@
         <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AA14" t="n">
         <v>1.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="N15" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.70833333334</v>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.99</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
-        <v>2.94</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.73</v>
+        <v>11</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.99</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>3.72</v>
       </c>
       <c r="O5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.85</v>
+        <v>5.77</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46044.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.79</v>
+        <v>2.34</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="N12" t="n">
-        <v>4.75</v>
+        <v>3.14</v>
       </c>
       <c r="O12" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>12</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.59</v>
+        <v>4.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
         <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.18</v>
+        <v>2.41</v>
       </c>
       <c r="M14" t="n">
-        <v>6.5</v>
+        <v>3.48</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.53</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>9</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AB14" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>1.18</v>
       </c>
       <c r="M15" t="n">
-        <v>3.48</v>
+        <v>6.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2325,61 +2325,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.73</v>
+        <v>3.4</v>
       </c>
       <c r="M16" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="N16" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="O16" t="n">
-        <v>5.1</v>
+        <v>4.86</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="S16" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="T16" t="n">
         <v>4.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
         <v>11</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
         <v>1.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC16" t="n">
         <v>6.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE16" t="n">
         <v>2.38</v>
@@ -2388,7 +2388,7 @@
         <v>1.51</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
         <v>1.25</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.99</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>2.94</v>
       </c>
       <c r="N4" t="n">
-        <v>11</v>
+        <v>3.73</v>
       </c>
       <c r="O4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" t="n">
         <v>1.99</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
         <v>2.7</v>
@@ -1748,19 +1748,19 @@
         <v>5.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
         <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="W11" t="n">
         <v>1.04</v>
@@ -1769,16 +1769,16 @@
         <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AC11" t="n">
         <v>5.77</v>
@@ -1793,10 +1793,10 @@
         <v>1.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46044.5</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="M12" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N12" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="O12" t="n">
         <v>3</v>
@@ -1873,13 +1873,13 @@
         <v>2.26</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>1.05</v>
@@ -1891,16 +1891,16 @@
         <v>1.48</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.85</v>
+        <v>4.97</v>
       </c>
       <c r="AD12" t="n">
         <v>1.11</v>
@@ -1915,7 +1915,7 @@
         <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.41</v>
+        <v>1.18</v>
       </c>
       <c r="M14" t="n">
-        <v>3.48</v>
+        <v>6.5</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.18</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
-        <v>6.5</v>
+        <v>3.48</v>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.53</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>9</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AB15" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="M16" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="N16" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="O16" t="n">
         <v>4.86</v>
@@ -2343,7 +2343,7 @@
         <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S16" t="n">
         <v>2.02</v>
@@ -2352,34 +2352,34 @@
         <v>4.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="V16" t="n">
         <v>11</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
         <v>1.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC16" t="n">
         <v>6.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE16" t="n">
         <v>2.38</v>
@@ -2388,7 +2388,7 @@
         <v>1.51</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
         <v>1.25</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" t="n">
         <v>1.99</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.99</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>3.73</v>
       </c>
       <c r="O5" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.18</v>
+        <v>2.41</v>
       </c>
       <c r="M14" t="n">
-        <v>6.5</v>
+        <v>3.48</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.53</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>9</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AB14" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>1.18</v>
       </c>
       <c r="M15" t="n">
-        <v>3.48</v>
+        <v>6.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.19</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.81</v>
+        <v>4.2</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46044.39583333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>2.19</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2</v>
+        <v>2.81</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1620,64 +1620,64 @@
         <v>2.62</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="N11" t="n">
-        <v>4.75</v>
+        <v>3.04</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.1</v>
+        <v>4.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="T11" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.77</v>
+        <v>4.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.42</v>
+        <v>2.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.81</v>
+        <v>1.46</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46044.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.32</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>3.04</v>
+        <v>4.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T12" t="n">
         <v>3.7</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.58</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.97</v>
+        <v>5.77</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.41</v>
+        <v>1.18</v>
       </c>
       <c r="M14" t="n">
-        <v>3.48</v>
+        <v>6.5</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.18</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
-        <v>6.5</v>
+        <v>3.48</v>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.53</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>9</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AB15" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2340,7 +2340,7 @@
         <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="R16" t="n">
         <v>1.7</v>
@@ -2379,7 +2379,7 @@
         <v>6.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE16" t="n">
         <v>2.38</v>
@@ -2391,7 +2391,7 @@
         <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46044.625</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>2.1</v>
@@ -2593,10 +2593,10 @@
         <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>5.5</v>
+        <v>6.35</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
         <v>1.05</v>
@@ -2605,19 +2605,19 @@
         <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
         <v>1.87</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>2.19</v>
       </c>
       <c r="M3" t="n">
-        <v>4.2</v>
+        <v>2.81</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46044.39583333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.19</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>2.81</v>
+        <v>4.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1971,10 +1971,10 @@
         <v>1.73</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="O13" t="n">
         <v>2.28</v>
@@ -1989,10 +1989,10 @@
         <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
         <v>1.36</v>
@@ -2010,10 +2010,10 @@
         <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB13" t="n">
         <v>1.85</v>
@@ -2034,7 +2034,7 @@
         <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46044.51041666666</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M14" t="n">
         <v>6.5</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="O14" t="n">
         <v>1.53</v>
@@ -2108,7 +2108,7 @@
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="T14" t="n">
         <v>2.01</v>
@@ -2117,7 +2117,7 @@
         <v>1.71</v>
       </c>
       <c r="V14" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="W14" t="n">
         <v>1.17</v>
@@ -2126,10 +2126,10 @@
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.25</v>
+        <v>5.65</v>
       </c>
       <c r="AA14" t="n">
         <v>1.42</v>
@@ -2141,19 +2141,19 @@
         <v>1.96</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="M15" t="n">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>1.73</v>
       </c>
       <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.1</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.8</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.73</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.19</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
-        <v>2.81</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>7.25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46044.39583333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>2.19</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2</v>
+        <v>2.81</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1022,7 +1022,7 @@
         <v>2.94</v>
       </c>
       <c r="N5" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="M8" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>4.46</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>7.12</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AB8" t="n">
         <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.12</v>
+        <v>4.41</v>
       </c>
       <c r="R9" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z9" t="n">
         <v>2.2</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V9" t="n">
-        <v>11</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AA9" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH9" t="n">
-        <v>2.06</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.62</v>
+        <v>1.86</v>
       </c>
       <c r="M10" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="N10" t="n">
-        <v>2.62</v>
+        <v>4.46</v>
       </c>
       <c r="O10" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.84</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1730,34 +1730,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="M11" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>3.04</v>
+        <v>2.84</v>
       </c>
       <c r="O11" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.12</v>
+        <v>3.98</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T11" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
         <v>10</v>
@@ -1766,37 +1766,37 @@
         <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.85</v>
+        <v>5.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AG11" t="n">
         <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46044.5</v>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="N12" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="O12" t="n">
         <v>2.7</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.05</v>
+        <v>5.92</v>
       </c>
       <c r="R12" t="n">
         <v>1.65</v>
@@ -1873,7 +1873,7 @@
         <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="U12" t="n">
         <v>1.17</v>
@@ -1888,19 +1888,19 @@
         <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.77</v>
+        <v>5.9</v>
       </c>
       <c r="AD12" t="n">
         <v>1.08</v>
@@ -1912,10 +1912,10 @@
         <v>1.49</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46044.5</v>
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.73</v>
+        <v>3.79</v>
       </c>
       <c r="M16" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="N16" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>4.86</v>
+        <v>5.1</v>
       </c>
       <c r="P16" t="n">
         <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="R16" t="n">
         <v>1.7</v>
@@ -2364,16 +2364,16 @@
         <v>1.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AC16" t="n">
         <v>6.05</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="M2" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46044.29166666666</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N3" t="n">
-        <v>7.25</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
         <v>1.97</v>
@@ -823,10 +823,10 @@
         <v>2.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
         <v>3.34</v>
@@ -1022,7 +1022,7 @@
         <v>2.94</v>
       </c>
       <c r="N5" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,61 +1254,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="M7" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.84</v>
+        <v>4.41</v>
       </c>
       <c r="R7" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="U7" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="V7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.65</v>
+        <v>5.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
         <v>2.24</v>
@@ -1317,10 +1317,10 @@
         <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V9" t="n">
+        <v>11</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z9" t="n">
         <v>2.35</v>
       </c>
-      <c r="M9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AA9" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="M10" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>4.46</v>
+        <v>6.23</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>5.37</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="N11" t="n">
-        <v>2.84</v>
+        <v>3.04</v>
       </c>
       <c r="O11" t="n">
         <v>3.4</v>
@@ -1769,16 +1769,16 @@
         <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
         <v>5.15</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="O12" t="n">
         <v>2.7</v>
@@ -1888,16 +1888,16 @@
         <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
         <v>5.9</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="M16" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="O16" t="n">
         <v>5.1</v>
@@ -2364,16 +2364,16 @@
         <v>1.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AC16" t="n">
         <v>6.05</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.65</v>
+        <v>4.42</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.1</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>2.37</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.8</v>
+        <v>2.14</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="N21" t="n">
-        <v>1.73</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,17 +3273,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="O2" t="n">
-        <v>3.62</v>
+        <v>4.68</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="R2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="S2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE2" t="n">
         <v>2.2</v>
       </c>
-      <c r="T2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AF2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46044.29166666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>2.19</v>
       </c>
       <c r="M3" t="n">
-        <v>4.2</v>
+        <v>2.81</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46044.39583333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.19</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>2.81</v>
+        <v>4.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AB6" t="n">
         <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="M9" t="n">
         <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>2.33</v>
+        <v>2.91</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.12</v>
+        <v>5.07</v>
       </c>
       <c r="R9" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="T9" t="n">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="U9" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.84</v>
+        <v>2.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.75</v>
+        <v>6.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.06</v>
+        <v>1.59</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="N10" t="n">
-        <v>6.23</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.37</v>
+        <v>4.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="T10" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="V10" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>3.04</v>
+        <v>4.86</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V11" t="n">
+        <v>12</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.79</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>10</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.42</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46044.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.79</v>
+        <v>2.65</v>
       </c>
       <c r="M12" t="n">
         <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="O12" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.92</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="T12" t="n">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.79</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46044.5</v>
@@ -1968,34 +1968,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="O13" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="Q13" t="n">
         <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
         <v>6.5</v>
@@ -2007,16 +2007,16 @@
         <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
         <v>3.2</v>
@@ -2025,16 +2025,16 @@
         <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46044.51041666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.19</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>11.5</v>
+        <v>2.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.14</v>
+        <v>1.17</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>7.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.53</v>
+        <v>11.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="M16" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="N16" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
         <v>5.1</v>
@@ -2340,7 +2340,7 @@
         <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="R16" t="n">
         <v>1.7</v>
@@ -2352,10 +2352,10 @@
         <v>4.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
@@ -2364,34 +2364,34 @@
         <v>1.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AC16" t="n">
         <v>6.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AF16" t="n">
         <v>1.51</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46044.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,22 +2801,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,17 +3273,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="M3" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>3.73</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>2.19</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2</v>
+        <v>2.81</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.99</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>2.94</v>
+        <v>4.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3.73</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>2.65</v>
       </c>
       <c r="M11" t="n">
         <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>4.86</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="T11" t="n">
-        <v>3.98</v>
+        <v>3.72</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.61</v>
       </c>
-      <c r="Z11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.79</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46044.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="M12" t="n">
         <v>2.85</v>
       </c>
       <c r="N12" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="O12" t="n">
         <v>2.7</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>3.72</v>
+        <v>3.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.46</v>
+        <v>2.23</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.17</v>
       </c>
       <c r="M14" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="N14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.9</v>
       </c>
-      <c r="N14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.62</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.17</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>7.11</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>11.5</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.96</v>
+        <v>1.44</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.84</v>
+        <v>2.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.14</v>
+        <v>4.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.26</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>3.05</v>
+        <v>1.78</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,22 +2801,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.42</v>
+        <v>2.16</v>
       </c>
       <c r="M20" t="n">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>3.08</v>
       </c>
       <c r="O20" t="n">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.88</v>
+        <v>5.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -784,7 +784,7 @@
         <v>2.94</v>
       </c>
       <c r="N3" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.19</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>2.81</v>
+        <v>4.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>2.19</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2</v>
+        <v>2.81</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1290,19 +1290,19 @@
         <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y7" t="n">
         <v>1.65</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
         <v>5.95</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.07</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="T9" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W9" t="n">
         <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AB9" t="n">
         <v>1.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.45</v>
+        <v>7.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46044.41666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="M17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3.5</v>
       </c>
-      <c r="N17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
         <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
         <v>4.75</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,22 +2801,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.16</v>
+        <v>3.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="N20" t="n">
-        <v>3.08</v>
+        <v>2.05</v>
       </c>
       <c r="O20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>1.57</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.05</v>
+        <v>5.75</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="M22" t="n">
         <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="O22" t="n">
         <v>5</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3167,25 +3167,25 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -3194,37 +3194,37 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46044.875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="M3" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="N3" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.99</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>3.72</v>
       </c>
       <c r="O4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.19</v>
+        <v>1.42</v>
       </c>
       <c r="M5" t="n">
-        <v>2.81</v>
+        <v>4.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.07</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AB8" t="n">
         <v>1.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.45</v>
+        <v>7.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>5.07</v>
       </c>
       <c r="R9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T9" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="U9" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="V9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
         <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AB9" t="n">
         <v>1.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.1</v>
+        <v>6.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46044.41666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.13</v>
+        <v>3.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M19" t="n">
         <v>4</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.6</v>
-      </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>5.75</v>
       </c>
       <c r="O19" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.37</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.05</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.57</v>
+        <v>2.13</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>5.75</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,26 +3035,26 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="P23" t="n">
         <v>1.87</v>
@@ -3206,7 +3206,7 @@
         <v>2.88</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC23" t="n">
         <v>5.6</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,26 +3273,26 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.19</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.81</v>
+        <v>4.2</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46044.39583333334</v>
@@ -903,7 +903,7 @@
         <v>2.94</v>
       </c>
       <c r="N4" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>2.19</v>
       </c>
       <c r="M5" t="n">
-        <v>4.1</v>
+        <v>2.81</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N6" t="n">
         <v>3</v>
       </c>
-      <c r="N6" t="n">
-        <v>4.6</v>
-      </c>
       <c r="O6" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.78</v>
+        <v>4.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="V6" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AA6" t="n">
         <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.95</v>
+        <v>5.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="M9" t="n">
         <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.07</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="T9" t="n">
-        <v>4.15</v>
+        <v>4.55</v>
       </c>
       <c r="U9" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W9" t="n">
         <v>1.02</v>
       </c>
       <c r="X9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AE9" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,34 +1611,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="M10" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.3</v>
+        <v>5.07</v>
       </c>
       <c r="R10" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="S10" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="T10" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="U10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="V10" t="n">
         <v>10</v>
@@ -1647,37 +1647,37 @@
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.6</v>
+        <v>6.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="O11" t="n">
         <v>3.25</v>
@@ -1745,10 +1745,10 @@
         <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
         <v>2.22</v>
@@ -1760,7 +1760,7 @@
         <v>1.2</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
@@ -1769,19 +1769,19 @@
         <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.2</v>
+        <v>5.35</v>
       </c>
       <c r="AD11" t="n">
         <v>1.1</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
         <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="O12" t="n">
         <v>2.7</v>
@@ -1867,16 +1867,16 @@
         <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S12" t="n">
         <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="V12" t="n">
         <v>12</v>
@@ -1885,25 +1885,25 @@
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
         <v>2.5</v>
@@ -1915,7 +1915,7 @@
         <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.17</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>7.11</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>11.5</v>
+        <v>2.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.96</v>
+        <v>1.44</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.84</v>
+        <v>2.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>1.17</v>
       </c>
       <c r="M15" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>9</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S15" t="n">
         <v>3.9</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.62</v>
+        <v>1.84</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="M16" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="O16" t="n">
         <v>5.1</v>
@@ -2340,13 +2340,13 @@
         <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S16" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="T16" t="n">
         <v>4.15</v>
@@ -2361,19 +2361,19 @@
         <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AC16" t="n">
         <v>6.05</v>
@@ -2388,7 +2388,7 @@
         <v>1.51</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AH16" t="n">
         <v>1.25</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,55 +2444,55 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
         <v>3.6</v>
       </c>
-      <c r="M17" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>2.05</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.57</v>
+        <v>2.13</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>5.75</v>
+        <v>3.05</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.13</v>
+        <v>1.57</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>5.75</v>
       </c>
       <c r="O21" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.70833333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3048,25 +3048,25 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3075,37 +3075,37 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46044.875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,38 +3154,38 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.06</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.35</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -3194,37 +3194,37 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46044.875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,26 +3273,26 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="M2" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="O2" t="n">
-        <v>4.68</v>
+        <v>4.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.77</v>
+        <v>3.06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V2" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
         <v>1.53</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AD2" t="n">
         <v>1.09</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46044.29166666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="M3" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.97</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46044.39583333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.99</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>2.94</v>
+        <v>4.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3.73</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="M5" t="n">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,61 +1492,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.63</v>
+        <v>2.06</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
-        <v>2.6</v>
+        <v>2.93</v>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="S9" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="T9" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="U9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="V9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
         <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AC9" t="n">
         <v>7.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
         <v>2.5</v>
@@ -1555,10 +1555,10 @@
         <v>1.45</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.07</v>
+        <v>4.76</v>
       </c>
       <c r="R10" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="T10" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="U10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V10" t="n">
+        <v>19</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.16</v>
       </c>
-      <c r="V10" t="n">
-        <v>10</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.39</v>
+        <v>2.71</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.32</v>
+        <v>1.79</v>
       </c>
       <c r="M11" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>3.04</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.68</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V11" t="n">
+        <v>12</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.5</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46044.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.79</v>
       </c>
-      <c r="M12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.96</v>
-      </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="U12" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="AG12" t="n">
         <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.77</v>
+        <v>1.38</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46044.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.17</v>
       </c>
       <c r="M14" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="N14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.9</v>
       </c>
-      <c r="N14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.62</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.17</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>7.11</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>11.5</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.96</v>
+        <v>1.44</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.84</v>
+        <v>2.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2343,22 +2343,22 @@
         <v>3.16</v>
       </c>
       <c r="R16" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="S16" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="T16" t="n">
         <v>4.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="V16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
         <v>1.16</v>
@@ -2388,10 +2388,10 @@
         <v>1.51</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46044.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.05</v>
+        <v>5.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,22 +2801,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>5.75</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
         <v>2.1</v>
@@ -2938,13 +2938,13 @@
         <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U21" t="n">
         <v>1.41</v>
@@ -2968,7 +2968,7 @@
         <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
         <v>3.1</v>
@@ -2977,10 +2977,10 @@
         <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
         <v>1.12</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3048,25 +3048,25 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3075,37 +3075,37 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46044.875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,38 +3154,38 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>4.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -3194,37 +3194,37 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.9</v>
+        <v>2.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>1.34</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46044.875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46044.875</v>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI24"/>
+  <dimension ref="A1:AI22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,31 +659,31 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="N2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="O2" t="n">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="U2" t="n">
         <v>1.19</v>
@@ -692,34 +692,34 @@
         <v>9.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
         <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Z2" t="n">
         <v>2.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG2" t="n">
         <v>1.32</v>
@@ -737,7 +737,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,76 +778,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V3" t="n">
+        <v>10</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.6</v>
       </c>
-      <c r="N3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
       <c r="AI3" s="3" t="n">
-        <v>46044.39583333334</v>
+        <v>46044.33333333334</v>
       </c>
     </row>
     <row r="4">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>2.62</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2</v>
+        <v>2.58</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>2.13</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.65</v>
+        <v>4.78</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>1.81</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V4" t="n">
+        <v>21</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE4" t="n">
         <v>2.9</v>
       </c>
-      <c r="U4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.79</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="N5" t="n">
         <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>19</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AA7" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.47</v>
+        <v>2.71</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.74</v>
+        <v>1.34</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1373,34 +1373,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>4.05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="P8" t="n">
         <v>1.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
         <v>1.73</v>
       </c>
       <c r="S8" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="T8" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="V8" t="n">
         <v>15</v>
@@ -1412,16 +1412,16 @@
         <v>1.17</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AC8" t="n">
         <v>7.1</v>
@@ -1430,16 +1430,16 @@
         <v>1.08</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,76 +1492,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>4.63</v>
       </c>
       <c r="O9" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
         <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.9</v>
+        <v>4.74</v>
       </c>
       <c r="R9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V9" t="n">
+        <v>12</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.66</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V9" t="n">
-        <v>13</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.67</v>
-      </c>
       <c r="Z9" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.1</v>
+        <v>6.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46044.41666666666</v>
+        <v>46044.5</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>2.39</v>
       </c>
       <c r="O10" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.76</v>
+        <v>3.26</v>
       </c>
       <c r="R10" t="n">
-        <v>1.84</v>
+        <v>1.61</v>
       </c>
       <c r="S10" t="n">
-        <v>1.84</v>
+        <v>2.17</v>
       </c>
       <c r="T10" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>19</v>
+        <v>9.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.35</v>
       </c>
-      <c r="AC10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46044.41666666666</v>
+        <v>46044.5</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>3.98</v>
+        <v>2.78</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.37</v>
+        <v>1.84</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.03</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46044.5</v>
+        <v>46044.51041666666</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="M12" t="n">
-        <v>2.78</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.04</v>
+        <v>2.61</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.35</v>
+        <v>2.17</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.1</v>
+        <v>1.61</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>2.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46044.5</v>
+        <v>46044.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.68</v>
+        <v>1.21</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.65</v>
+        <v>15</v>
       </c>
       <c r="O13" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="S13" t="n">
-        <v>2.95</v>
+        <v>3.96</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="U13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1.38</v>
       </c>
-      <c r="V13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AB13" t="n">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.2</v>
+        <v>1.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.02</v>
+        <v>4.6</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46044.51041666666</v>
+        <v>46044.60416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.17</v>
+        <v>3.73</v>
       </c>
       <c r="M14" t="n">
-        <v>7.11</v>
+        <v>2.62</v>
       </c>
       <c r="N14" t="n">
-        <v>11.5</v>
+        <v>2.13</v>
       </c>
       <c r="O14" t="n">
-        <v>1.53</v>
+        <v>5.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>3.16</v>
       </c>
       <c r="R14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V14" t="n">
+        <v>11</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.2</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AI14" s="3" t="n">
-        <v>46044.60416666666</v>
+        <v>46044.625</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2251,22 +2251,22 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>1.64</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46044.60416666666</v>
+        <v>46044.70833333334</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.73</v>
+        <v>2.13</v>
       </c>
       <c r="M16" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.13</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>5.1</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V16" t="n">
-        <v>11</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AC16" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46044.625</v>
+        <v>46044.70833333334</v>
       </c>
     </row>
     <row r="17">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.28</v>
+        <v>3.38</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N18" t="n">
-        <v>5.2</v>
+        <v>2.05</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.13</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.05</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2797,26 +2797,26 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46044.70833333334</v>
+        <v>46044.875</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,80 +2916,80 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>2.89</v>
+        <v>2.12</v>
       </c>
       <c r="T21" t="n">
-        <v>2.69</v>
+        <v>4.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC21" t="n">
         <v>5.6</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46044.70833333334</v>
+        <v>46044.875</v>
       </c>
     </row>
     <row r="22">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,317 +3035,79 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46044.875</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46044</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI23" s="3" t="n">
-        <v>46044.875</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46044</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Mount Pleasant Academy FC</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O24" t="n">
-        <v>5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI24" s="3" t="n">
         <v>46044.875</v>
       </c>
     </row>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.78</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="S4" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="V4" t="n">
-        <v>21</v>
+        <v>9.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.22</v>
       </c>
-      <c r="Y4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="M5" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.5</v>
+        <v>4.78</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="S5" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="T5" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="V5" t="n">
-        <v>9.9</v>
+        <v>21</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AF5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="O6" t="n">
-        <v>3.04</v>
+        <v>2.68</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="S6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T6" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
         <v>15</v>
@@ -1171,37 +1171,37 @@
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
         <v>3.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.84</v>
+        <v>2.15</v>
       </c>
       <c r="M7" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.99</v>
+        <v>4.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="S7" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="T7" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="U7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V7" t="n">
+        <v>15</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.1</v>
       </c>
-      <c r="V7" t="n">
-        <v>19</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.25</v>
+        <v>7.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.87</v>
+        <v>2.84</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="N8" t="n">
-        <v>4.05</v>
+        <v>3.36</v>
       </c>
       <c r="O8" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="R8" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="S8" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="T8" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="V8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="Z8" t="n">
         <v>2</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.1</v>
+        <v>6.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="N9" t="n">
-        <v>4.63</v>
+        <v>2.39</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.74</v>
+        <v>3.26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="T9" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="AA9" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
         <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.44</v>
+        <v>5.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG9" t="n">
         <v>1.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46044.5</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.39</v>
+        <v>4.63</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.26</v>
+        <v>4.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="S10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V10" t="n">
+        <v>12</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2.17</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AA10" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AB10" t="n">
         <v>1.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.65</v>
+        <v>6.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
         <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46044.5</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,55 +2325,55 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.13</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.65</v>
+        <v>3.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.38</v>
+        <v>2.28</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.05</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.28</v>
+        <v>3.38</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2797,77 +2797,77 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46044.875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46044.875</v>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -761,20 +761,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="M4" t="n">
-        <v>2.68</v>
+        <v>2.43</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>4.78</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="S4" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="T4" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="V4" t="n">
-        <v>9.9</v>
+        <v>21</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AF4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="M5" t="n">
-        <v>2.58</v>
+        <v>2.23</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.78</v>
+        <v>5.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="S5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.81</v>
       </c>
-      <c r="T5" t="n">
-        <v>5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V5" t="n">
-        <v>21</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="AA5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.22</v>
       </c>
-      <c r="Y5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.68</v>
+        <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="S6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="V6" t="n">
         <v>15</v>
@@ -1171,37 +1171,37 @@
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="n">
         <v>3.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,60 +1228,60 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="O7" t="n">
-        <v>3.04</v>
+        <v>2.68</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="S7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T7" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="V7" t="n">
         <v>15</v>
@@ -1290,37 +1290,37 @@
         <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="n">
         <v>3.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="M9" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="N9" t="n">
-        <v>2.39</v>
+        <v>3.04</v>
       </c>
       <c r="O9" t="n">
         <v>3.75</v>
@@ -1531,16 +1531,16 @@
         <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AC9" t="n">
         <v>5.65</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N10" t="n">
-        <v>4.63</v>
+        <v>4.75</v>
       </c>
       <c r="O10" t="n">
         <v>2.8</v>
@@ -1650,16 +1650,16 @@
         <v>1.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AC10" t="n">
         <v>6.44</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.13</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
         <v>3.6</v>
       </c>
-      <c r="M17" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA17" t="n">
         <v>2.05</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>3.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>2.05</v>
       </c>
       <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V18" t="n">
+        <v>12</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE18" t="n">
         <v>2.1</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.37</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2797,77 +2797,77 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>4.35</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>2.71</v>
+        <v>2.12</v>
       </c>
       <c r="T20" t="n">
-        <v>2.79</v>
+        <v>4.15</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.25</v>
+        <v>2.14</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>2.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>1.34</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.15</v>
+        <v>5.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46044.875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O21" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.35</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>2.12</v>
+        <v>2.71</v>
       </c>
       <c r="T21" t="n">
-        <v>4.15</v>
+        <v>2.79</v>
       </c>
       <c r="U21" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.6</v>
+        <v>3.15</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.875</v>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -999,20 +999,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1109,99 +1109,99 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.15</v>
+        <v>2.84</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="N6" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="O6" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="Q6" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T6" t="n">
         <v>4.8</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4.45</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="V6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.2</v>
+        <v>6.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,34 +1254,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.68</v>
+        <v>3.04</v>
       </c>
       <c r="P7" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="S7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T7" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="U7" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="V7" t="n">
         <v>15</v>
@@ -1290,37 +1290,37 @@
         <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
         <v>3.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.84</v>
+        <v>1.87</v>
       </c>
       <c r="M8" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
-        <v>3.36</v>
+        <v>4.05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="S8" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="T8" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="V8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="Z8" t="n">
         <v>2</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.25</v>
+        <v>7.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.34</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1475,20 +1475,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1594,20 +1594,20 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1713,87 +1713,87 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
         <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="R11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.4</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
         <v>2.02</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.24</v>
+        <v>1.12</v>
       </c>
       <c r="M12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V12" t="n">
         <v>3.8</v>
       </c>
-      <c r="N12" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="W12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB12" t="n">
         <v>3</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AC12" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46044.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.21</v>
+        <v>2.24</v>
       </c>
       <c r="M13" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>15</v>
+        <v>2.61</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>3.96</v>
+        <v>3.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="V13" t="n">
-        <v>3.94</v>
+        <v>4.9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.92</v>
+        <v>2.39</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.6</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46044.60416666666</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.73</v>
+        <v>3.55</v>
       </c>
       <c r="M14" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="N14" t="n">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="O14" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="S14" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="T14" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
         <v>11</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.05</v>
+        <v>6.15</v>
       </c>
       <c r="AD14" t="n">
         <v>1.06</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AF14" t="n">
         <v>1.51</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46044.625</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3.2</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AA15" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.13</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AG16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,34 +2444,34 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="O17" t="n">
-        <v>4.75</v>
+        <v>2.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.37</v>
+        <v>5.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
         <v>8.5</v>
@@ -2480,37 +2480,37 @@
         <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE17" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.05</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.95</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3</v>
+        <v>2.89</v>
       </c>
       <c r="T18" t="n">
-        <v>3.45</v>
+        <v>2.69</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.55</v>
+        <v>1.12</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.28</v>
+        <v>2.25</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>3.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>2.05</v>
       </c>
       <c r="O19" t="n">
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V19" t="n">
+        <v>12</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE19" t="n">
         <v>2.1</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.84</v>
+        <v>1.87</v>
       </c>
       <c r="M6" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>3.36</v>
+        <v>4.05</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="P6" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="S6" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="T6" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="Z6" t="n">
         <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.25</v>
+        <v>7.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.34</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,22 +1347,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.87</v>
+        <v>2.84</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="N8" t="n">
-        <v>4.05</v>
+        <v>3.36</v>
       </c>
       <c r="O8" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="R8" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="S8" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="T8" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="V8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="Z8" t="n">
         <v>2</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.1</v>
+        <v>6.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1466,22 +1466,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.32</v>
+        <v>1.79</v>
       </c>
       <c r="M9" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N9" t="n">
-        <v>3.04</v>
+        <v>4.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.26</v>
+        <v>4.74</v>
       </c>
       <c r="R9" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="S9" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="T9" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="V9" t="n">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.65</v>
+        <v>6.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG9" t="n">
         <v>1.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46044.5</v>
@@ -1585,22 +1585,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="M10" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="N10" t="n">
-        <v>4.75</v>
+        <v>3.04</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.74</v>
+        <v>3.26</v>
       </c>
       <c r="R10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="S10" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="T10" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.44</v>
+        <v>5.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG10" t="n">
         <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46044.5</v>
@@ -1832,20 +1832,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1951,20 +1951,20 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.13</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AG15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>1.53</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="O16" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.37</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>3.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>2.05</v>
       </c>
       <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V18" t="n">
+        <v>12</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE18" t="n">
         <v>2.1</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.6</v>
+        <v>2.13</v>
       </c>
       <c r="M19" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="AB19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC19" t="n">
         <v>3.45</v>
       </c>
-      <c r="U19" t="n">
+      <c r="AD19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.25</v>
       </c>
-      <c r="V19" t="n">
-        <v>12</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2797,77 +2797,77 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.35</v>
+        <v>2.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>2.12</v>
+        <v>2.71</v>
       </c>
       <c r="T20" t="n">
-        <v>4.15</v>
+        <v>2.79</v>
       </c>
       <c r="U20" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.6</v>
+        <v>3.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46044.875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3048,25 +3048,25 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3075,37 +3075,37 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46044.875</v>

--- a/jogos_2026-01-22.xlsx
+++ b/jogos_2026-01-22.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -886,10 +886,10 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="M4" t="n">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="N4" t="n">
-        <v>3.79</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.78</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="S4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.81</v>
       </c>
-      <c r="T4" t="n">
-        <v>5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V4" t="n">
-        <v>21</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.22</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46044.39583333334</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1005,10 +1005,10 @@
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="M5" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>3.79</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.5</v>
+        <v>4.78</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="S5" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="T5" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="V5" t="n">
-        <v>9.9</v>
+        <v>21</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AF5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46044.39583333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.87</v>
+        <v>2.84</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="N6" t="n">
-        <v>4.05</v>
+        <v>3.36</v>
       </c>
       <c r="O6" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="R6" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="S6" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="V6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="Z6" t="n">
         <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.1</v>
+        <v>6.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46044.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,22 +1347,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.84</v>
+        <v>1.87</v>
       </c>
       <c r="M8" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
-        <v>3.36</v>
+        <v>4.05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="S8" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="T8" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="V8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="Z8" t="n">
         <v>2</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.25</v>
+        <v>7.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.34</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46044.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,99 +2180,99 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>1.53</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="O15" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.37</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,99 +2299,99 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.53</v>
+        <v>3.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.88</v>
+        <v>2.95</v>
       </c>
       <c r="N16" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="O16" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>12</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE16" t="n">
         <v>2.1</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2418,99 +2418,99 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
         <v>3.2</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AA17" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,74 +2559,74 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" t="n">
         <v>3.6</v>
       </c>
-      <c r="M18" t="n">
-        <v>2.95</v>
-      </c>
       <c r="N18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.05</v>
       </c>
-      <c r="O18" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V18" t="n">
-        <v>12</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="n">
         <v>1.28</v>
@@ -2656,19 +2656,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2.13</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V19" t="n">
-        <v>7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46044.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2797,77 +2797,77 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46044.875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2929,25 +2929,25 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2956,37 +2956,37 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46044.875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.9</v>
       </c>
-      <c r="P22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4.15</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.13</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46044.875</v>
